--- a/data_extactor/batch_10_fa/trimmed/batch_0030_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0030_fa_trim.xlsx
@@ -508,12 +508,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | امور اداری | رایانه و الکترونیک | ارتباطات و رسانه</t>
+          <t>قانون و دولت | زبان انگلیسی | خدمات مشتری و شخصی | اداری | رایانه و الکترونیک | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | داوران، میانجی‌گران و صلح‌یاران | قضات دادگاه و دادیاران | کارشناسان پژوهش و تحریر قضایی (دستیاران قضایی) | استادان حقوق، آموزش عالی | کارشناسان و دستیاران امور حقوقی (دستیاران حقوقی) | کارشناسان بررسی اسناد مالکیت و خلاصه برداری اسناد ثبتی</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | داوران، میانجی‌گران و صلح‌یاران | قضات دادگاه و دادیاران | کارشناسان پژوهش و تحریر قضایی | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و دستیاران امور حقوقی | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | زبان انگلیسی | امور اداری</t>
+          <t>قانون و دولت | زبان انگلیسی | اداری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | کارمندان دادگاه، شهرداری و امور ثبت و پروانه | قضات دادگاه و دادیاران | استادان حقوق، آموزش عالی | وکلا | دبیران و مسئولان دفاتر حقوقی | کارشناسان و دستیاران امور حقوقی (دستیاران حقوقی)</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | قضات دادگاه و دادیاران | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | وکلا | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان و دستیاران امور حقوقی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | امور اداری | پزشکی و دندانپزشکی | مدیریت و امور اداری</t>
+          <t>قانون و دولت | زبان انگلیسی | خدمات مشتری و شخصی | اداری | پزشکی و دندان‌پزشکی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>داوران، میانجی‌گران و صلح‌یاران | کارشناسان انطباق و نظارت قانونی | کارمندان دادگاه، شهرداری و امور ثبت و پروانه | قضات دادگاه و دادیاران | کارشناسان پژوهش و تحریر قضایی (دستیاران قضایی) | وکلا | کارشناسان و دستیاران امور حقوقی (دستیاران حقوقی)</t>
+          <t>داوران، میانجی‌گران و صلح‌یاران | کارشناسان پایش انطباق و بازرسی مقرراتی | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | قضات دادگاه و دادیاران | کارشناسان پژوهش و تحریر قضایی | وکلا | کارشناسان و دستیاران امور حقوقی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نگارش | سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال</t>
+          <t>گوش دادن فعال | نگارش | سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حقوق و مقررات دولتی | امور کارکنان و منابع انسانی | مدیریت و امور اداری</t>
+          <t>زبان انگلیسی | قانون و دولت | پرسنل و منابع انسانی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | مددکاران اجتماعی کودک، خانواده و مدرسه | کارشناسان انطباق و نظارت قانونی | قضات دادگاه و دادیاران | متخصصان روابط کار | وکلا | کارشناسان و دستیاران امور حقوقی (دستیاران حقوقی)</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | مددکاران اجتماعی کودک، خانواده و مدرسه | کارشناسان پایش انطباق و بازرسی مقرراتی | قضات دادگاه و دادیاران | کارشناسان روابط کار و امور تشکل‌های کارگری | وکلا | کارشناسان و دستیاران امور حقوقی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | زبان انگلیسی | مدیریت و امور اداری | روان‌شناسی | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی</t>
+          <t>قانون و دولت | زبان انگلیسی | مدیریت و اداره | روان‌شناسی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | داوران، میانجی‌گران و صلح‌یاران | کارمندان دادگاه، شهرداری و امور ثبت و پروانه | کارشناسان پژوهش و تحریر قضایی (دستیاران قضایی) | استادان حقوق، آموزش عالی | وکلا | کارشناسان و دستیاران امور حقوقی (دستیاران حقوقی)</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | داوران، میانجی‌گران و صلح‌یاران | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | کارشناسان پژوهش و تحریر قضایی | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | وکلا | کارشناسان و دستیاران امور حقوقی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>نگارش | درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>نگارش | درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | زبان انگلیسی | امور اداری | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری</t>
+          <t>قانون و دولت | زبان انگلیسی | اداری | رایانه و الکترونیک | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارشناسان انطباق و نظارت قانونی | کارمندان دادگاه، شهرداری و امور ثبت و پروانه | متصدیان بایگانی و ثبت اسناد | کارشناسان پژوهش و تحریر قضایی (دستیاران قضایی) | وکلا | دبیران و مسئولان دفاتر حقوقی | کارشناسان بررسی اسناد مالکیت و خلاصه برداری اسناد ثبتی</t>
+          <t>کارشناسان پایش انطباق و بازرسی مقرراتی | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | متصدیان بایگانی و اسناد | کارشناسان پژوهش و تحریر قضایی | وکلا | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حقوق و مقررات دولتی | امور اداری | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک</t>
+          <t>زبان انگلیسی | قانون و دولت | اداری | خدمات مشتری و شخصی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | دید نزدیک | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | بینایی نزدیک | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ارزیابان و قیمت‌گذاران املاک و مستغلات | کارمندان دادگاه، شهرداری و امور ثبت و پروانه | کارشناسان مدیریت اسناد | متصدیان بایگانی و ثبت اسناد | بازرسان و کارشناسان اموال دولتی | وکلا | کارشناسان و دستیاران امور حقوقی (دستیاران حقوقی)</t>
+          <t>کارشناسان ارزیابی و ممیزی املاک و مستغلات | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | کارشناسان مدیریت اسناد و مدارک | متصدیان بایگانی و اسناد | بازرسان و ممیزان اموال دولتی | وکلا | کارشناسان و دستیاران امور حقوقی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | زبان انگلیسی | مدیریت و امور اداری | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | ارتباطات و رسانه</t>
+          <t>قانون و دولت | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | خدمات مشتری و شخصی | اقتصاد و حسابداری | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کارشناسان و دستیاران امور حقوقی (دستیاران حقوقی) | کارشناسان بررسی اسناد مالکیت و خلاصه برداری اسناد ثبتی | کارشناسان پژوهش و تحریر قضایی (دستیاران قضایی) | وکلا | کارشناسان انطباق و نظارت قانونی | دبیران و مسئولان دفاتر حقوقی | کارشناسان مدیریت اسناد</t>
+          <t>کارشناسان و دستیاران امور حقوقی | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی | کارشناسان پژوهش و تحریر قضایی | وکلا | کارشناسان پایش انطباق و بازرسی مقرراتی | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان مدیریت اسناد و مدارک</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | راهبردهای یادگیری | نگارش | شنیدن فعال | درک مطلب | یادگیری فعال | تفکر انتقادی | نظارت | ریاضیات</t>
+          <t>سخن گفتن | راهبردهای یادگیری | نگارش | گوش دادن فعال | درک مطلب | یادگیری فعال | تفکر انتقادی | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | مدیریت و امور اداری | اقتصاد و حسابداری | ریاضیات | حقوق و مقررات دولتی | امور کارکنان و منابع انسانی</t>
+          <t>آموزش و پرورش | مدیریت و اداره | اقتصاد و حسابداری | ریاضیات | قانون و دولت | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مربیان و مدرسان فنی و حرفه‌ای، آموزش عالی | استادان اقتصاد، آموزش عالی | مدیران امور آموزشی، آموزش عالی | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | تحلیل‌گران و مشاوران مدیریت | دستیاران آموزشی و حل تمرین، آموزش عالی | کارشناسان آموزش و توسعه منابع انسانی</t>
+          <t>مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | استادان اقتصاد دانشگاه | مدیران آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | کارشناسان تحلیل مدیریت و روش‌ها | دستیاران آموزشی در آموزش عالی | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | درک مطلب | شنیدن فعال | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
+          <t>سخن گفتن | نگارش | درک مطلب | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | آموزش و تدریس | زبان انگلیسی | ریاضیات | مهندسی و فناوری | طراحی</t>
+          <t>رایانه و الکترونیک | آموزش و پرورش | زبان انگلیسی | ریاضیات | مهندسی و فناوری | طراحی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مهندسان سخت‌افزار رایانه | برنامه‌نویسان رایانه | تحلیل‌گران سیستم‌های رایانه‌ای | دانشمندان و پژوهشگران علوم رایانه و اطلاعات | استادان علوم مهندسی، آموزش عالی | استادان علوم ریاضی، آموزش عالی | توسعه‌دهندگان نرم‌افزار</t>
+          <t>مهندسان سخت‌افزار رایانه | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | پژوهشگران علوم رایانه و اطلاعات | استادان و مدرسان مهندسی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
